--- a/exemple-ePrescription/ig/StructureDefinition-fr-cda-sujet-non-humain.xlsx
+++ b/exemple-ePrescription/ig/StructureDefinition-fr-cda-sujet-non-humain.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$53</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1356" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="235">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T08:51:06+00:00</t>
+    <t>2026-05-06T11:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -577,6 +577,136 @@
   </si>
   <si>
     <t>RelatedSubject.code</t>
+  </si>
+  <si>
+    <t>Subject.relatedSubject.code.nullFlavor</t>
+  </si>
+  <si>
+    <t>Subject.relatedSubject.code.code</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>Subject.relatedSubject.code.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>Subject.relatedSubject.code.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>Subject.relatedSubject.code.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Subject.relatedSubject.code.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>Subject.relatedSubject.code.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>Subject.relatedSubject.code.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Subject.relatedSubject.code.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
+</t>
+  </si>
+  <si>
+    <t>The text or phrase used as the basis for the coding.</t>
+  </si>
+  <si>
+    <t>CD.originalText</t>
+  </si>
+  <si>
+    <t>Subject.relatedSubject.code.qualifier</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
+</t>
+  </si>
+  <si>
+    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
+  </si>
+  <si>
+    <t>CD.qualifier</t>
+  </si>
+  <si>
+    <t>Subject.relatedSubject.code.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CD
+</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
   </si>
   <si>
     <t>Subject.relatedSubject.addr</t>
@@ -926,7 +1056,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK42"/>
+  <dimension ref="A1:AK53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.30859375" customWidth="true" bestFit="true"/>
@@ -4942,7 +5072,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>183</v>
       </c>
@@ -4953,15 +5083,17 @@
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E40" s="2"/>
+      <c r="E40" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F40" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>161</v>
+        <v>74</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -4970,13 +5102,11 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>185</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>185</v>
+        <v>86</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5003,13 +5133,11 @@
         <v>74</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>74</v>
@@ -5027,13 +5155,13 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>186</v>
+        <v>89</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>74</v>
@@ -5045,26 +5173,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E41" s="2"/>
+      <c r="E41" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F41" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -5073,10 +5203,12 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>188</v>
+        <v>85</v>
       </c>
       <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
+      <c r="M41" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5126,13 +5258,13 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>74</v>
@@ -5144,26 +5276,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E42" s="2"/>
+      <c r="E42" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="F42" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>74</v>
@@ -5172,10 +5306,12 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>191</v>
+        <v>112</v>
       </c>
       <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
+      <c r="M42" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5225,26 +5361,1147 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E43" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="AG42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK42" t="s" s="2">
+      <c r="F43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L43" s="2"/>
+      <c r="M43" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E44" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L44" s="2"/>
+      <c r="M44" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E45" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L45" s="2"/>
+      <c r="M45" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L46" s="2"/>
+      <c r="M46" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L47" s="2"/>
+      <c r="M47" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E48" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="F48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L48" s="2"/>
+      <c r="M48" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E49" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="F49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L49" s="2"/>
+      <c r="M49" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E50" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="F50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L50" s="2"/>
+      <c r="M50" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK53" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK42">
+  <autoFilter ref="A1:AK53">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5254,7 +6511,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI41">
+  <conditionalFormatting sqref="A2:AI52">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
